--- a/HR_Block_PE_LBO_Model.xlsx
+++ b/HR_Block_PE_LBO_Model.xlsx
@@ -333,7 +333,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>H&amp;R BLOCK | PUBLIC-TO-PRIVATE INVESTMENT CASE</x:v>
+        <x:v>H&amp;R BLOCK TAKE-PRIVATE CASE</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -365,7 +365,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="str">
-        <x:v>AS OF 22 OCTOBER 2026  •  HYPOTHETICAL TRANSACTION  •  USD MILLIONS</x:v>
+        <x:v>AS OF 22 OCTOBER 2026. HYPOTHETICAL TRANSACTION. USD MILLIONS.</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -387,7 +387,7 @@
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="9" t="str">
-        <x:v>UNDERWRITING SNAPSHOT</x:v>
+        <x:v>TRANSACTION SUMMARY</x:v>
       </x:c>
       <x:c r="B6" s="9"/>
       <x:c r="C6" s="9"/>
@@ -534,7 +534,7 @@
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="9" t="str">
-        <x:v>FIVE-YEAR INVESTMENT OUTCOMES</x:v>
+        <x:v>FIVE-YEAR SPONSOR RETURNS</x:v>
       </x:c>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
@@ -743,7 +743,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="str">
-        <x:v>Key rationale: stable cash flow and modest capital intensity, but acquisition premium + borrowing cost impair risk-adjusted returns.</x:v>
+        <x:v>Cash flow and low capital intensity support the case, but the purchase premium and borrowing costs reduce returns.</x:v>
       </x:c>
       <x:c r="B30" s="2"/>
       <x:c r="C30" s="2"/>
@@ -755,7 +755,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2" t="str">
-        <x:v>Key unresolved diligence: seasonal liquidity, tax policy, client retention, automation/AI, senior debt terms, cash accessibility.</x:v>
+        <x:v>Further diligence: seasonal liquidity, tax policy, client retention, AI competition, senior debt terms and available cash.</x:v>
       </x:c>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -767,7 +767,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2" t="str">
-        <x:v>This is a research case, not a live bid. All forecasts, financing rates, multiples and deal terms are illustrative.</x:v>
+        <x:v>Independent research case. Forecasts, financing rates, multiples and transaction terms are illustrative.</x:v>
       </x:c>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -803,7 +803,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>H&amp;R BLOCK | REPORTED FINANCIALS ($ MILLIONS)</x:v>
+        <x:v>H&amp;R BLOCK REPORTED FINANCIALS ($ MILLIONS)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -1118,7 +1118,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="str">
-        <x:v>FY2025 / FY2026 EBITDA reconciles to the company disclosed non-GAAP EBITDA.</x:v>
+        <x:v>FY2025 and FY2026 EBITDA reconcile to the company's disclosed non-GAAP EBITDA.</x:v>
       </x:c>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
@@ -1130,7 +1130,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="str">
-        <x:v>FY2025 FY2026 financial debt excludes operating leases.</x:v>
+        <x:v>FY2025 and FY2026 financial debt exclude operating leases.</x:v>
       </x:c>
       <x:c r="B22" s="2"/>
       <x:c r="C22" s="2"/>
@@ -1142,7 +1142,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="str">
-        <x:v>Annual cash flow is highly seasonal; June cash is not equivalent to free cash throughout the tax year.</x:v>
+        <x:v>Cash flow is seasonal. June cash does not establish the cash available throughout the tax year.</x:v>
       </x:c>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
@@ -1199,7 +1199,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>DEAL &amp; SCENARIO INPUTS | BLUE = EDITABLE</x:v>
+        <x:v>TRANSACTION AND SCENARIO INPUTS (BLUE = EDITABLE)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -1467,7 +1467,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="str">
-        <x:v>Sponsor holding period (years)</x:v>
+        <x:v>Hold period for sensitivity (years)</x:v>
       </x:c>
       <x:c r="B21" s="18" t="n">
         <x:v>5</x:v>
@@ -1575,7 +1575,7 @@
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
       <x:c r="A29" s="9" t="str">
-        <x:v>OPERATING SCENARIOS | ASSUMPTIONS, NOT GUIDANCE</x:v>
+        <x:v>OPERATING SCENARIO ASSUMPTIONS</x:v>
       </x:c>
       <x:c r="B29" s="9"/>
       <x:c r="C29" s="9"/>
@@ -1853,7 +1853,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="str">
-        <x:v>EBITDA vs adjusted EBITDA caveat: FY2027 guidance is adjusted, FY2026 reported historical metric is EBITDA.</x:v>
+        <x:v>FY2027 guidance uses adjusted EBITDA; FY2026 historical results use reported EBITDA. Definitions differ.</x:v>
       </x:c>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -1865,7 +1865,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="str">
-        <x:v>Lease liabilities, tax assets, stock compensation, seller rollover, and transaction structure require additional diligence.</x:v>
+        <x:v>Further diligence is needed on leases, tax assets, stock compensation, seller rollover and transaction structure.</x:v>
       </x:c>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -1877,7 +1877,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="str">
-        <x:v>The model assumes full reported cash is transaction-available subject to $500mm sponsor-funded minimum cash; verify foreign/seasonal constraints.</x:v>
+        <x:v>The model uses all reported cash at closing and funds $500mm of opening cash. Foreign and seasonal availability remain unverified.</x:v>
       </x:c>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -1925,7 +1925,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>TAKE-PRIVATE | SOURCES &amp; USES ($ MILLIONS)</x:v>
+        <x:v>TAKE-PRIVATE SOURCES AND USES ($ MILLIONS)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -2505,7 +2505,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2" t="str">
-        <x:v>Assumes debt refinance at book value, available unrestricted cash, no rollover, and no lease-debt capitalization.</x:v>
+        <x:v>Assumes debt refinancing at book value, all reported unrestricted cash available, no seller rollover and no lease-debt capitalization.</x:v>
       </x:c>
       <x:c r="B43" s="2"/>
       <x:c r="C43" s="2"/>
@@ -2517,7 +2517,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="str">
-        <x:v>These assumptions are educational; this is not a financing commitment or executable bid.</x:v>
+        <x:v>Financing rates and terms are illustrative; no lender commitment is assumed.</x:v>
       </x:c>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -2555,7 +2555,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>DOWNSIDE CASE | 5-YEAR LBO CASH FLOW AND DEBT SCHEDULE ($ MILLIONS)</x:v>
+        <x:v>DOWNSIDE LBO CASH FLOW AND DEBT ($ MILLIONS)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -3630,7 +3630,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="str">
-        <x:v>Cash interest on beginning-of-year debt; no revolver, M&amp;A outlays, OID, or tax shield limitation modeled.</x:v>
+        <x:v>Interest uses opening debt balances. No revolver, M&amp;A spending, OID or tax deductibility limit is modeled.</x:v>
       </x:c>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -3642,7 +3642,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="str">
-        <x:v>All non-mandatory debt paydown applies only to the first-lien term loan; senior notes mature as a bullet at exit.</x:v>
+        <x:v>All discretionary repayments reduce the first-lien term loan. Senior notes remain a bullet payment at exit.</x:v>
       </x:c>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -3654,7 +3654,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="str">
-        <x:v>Closing cash accumulation may conceal intrayear seasonality / minimum cash needs; confirm with monthly liquidity diligence.</x:v>
+        <x:v>Annual cash balances can miss seasonal funding needs. A monthly liquidity forecast is still needed.</x:v>
       </x:c>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -3692,7 +3692,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>BASE CASE | 5-YEAR LBO CASH FLOW AND DEBT SCHEDULE ($ MILLIONS)</x:v>
+        <x:v>BASE LBO CASH FLOW AND DEBT ($ MILLIONS)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -4767,7 +4767,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="str">
-        <x:v>Cash interest on beginning-of-year debt; no revolver, M&amp;A outlays, OID, or tax shield limitation modeled.</x:v>
+        <x:v>Interest uses opening debt balances. No revolver, M&amp;A spending, OID or tax deductibility limit is modeled.</x:v>
       </x:c>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -4779,7 +4779,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="str">
-        <x:v>All non-mandatory debt paydown applies only to the first-lien term loan; senior notes mature as a bullet at exit.</x:v>
+        <x:v>All discretionary repayments reduce the first-lien term loan. Senior notes remain a bullet payment at exit.</x:v>
       </x:c>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -4791,7 +4791,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="str">
-        <x:v>Closing cash accumulation may conceal intrayear seasonality / minimum cash needs; confirm with monthly liquidity diligence.</x:v>
+        <x:v>Annual cash balances can miss seasonal funding needs. A monthly liquidity forecast is still needed.</x:v>
       </x:c>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -4829,7 +4829,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>UPSIDE CASE | 5-YEAR LBO CASH FLOW AND DEBT SCHEDULE ($ MILLIONS)</x:v>
+        <x:v>UPSIDE LBO CASH FLOW AND DEBT ($ MILLIONS)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -5904,7 +5904,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="str">
-        <x:v>Cash interest on beginning-of-year debt; no revolver, M&amp;A outlays, OID, or tax shield limitation modeled.</x:v>
+        <x:v>Interest uses opening debt balances. No revolver, M&amp;A spending, OID or tax deductibility limit is modeled.</x:v>
       </x:c>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -5916,7 +5916,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="str">
-        <x:v>All non-mandatory debt paydown applies only to the first-lien term loan; senior notes mature as a bullet at exit.</x:v>
+        <x:v>All discretionary repayments reduce the first-lien term loan. Senior notes remain a bullet payment at exit.</x:v>
       </x:c>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -5928,7 +5928,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="str">
-        <x:v>Closing cash accumulation may conceal intrayear seasonality / minimum cash needs; confirm with monthly liquidity diligence.</x:v>
+        <x:v>Annual cash balances can miss seasonal funding needs. A monthly liquidity forecast is still needed.</x:v>
       </x:c>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -5966,7 +5966,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>BASE OPERATIONS | PRICE PREMIUM vs EXIT MULTIPLE</x:v>
+        <x:v>BASE-CASE IRR BY OFFER PREMIUM AND EXIT MULTIPLE</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -6004,7 +6004,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="str">
-        <x:v>Scenario: Base 2031 EBITDA, debt and cash; offer changes sponsor equity and deal fees only.</x:v>
+        <x:v>Base 2031 EBITDA, debt and cash stay fixed. The offer changes sponsor equity and transaction fees only.</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -6327,7 +6327,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2" t="str">
-        <x:v>Sensitivity holds base forecast debt and cash constant across transaction premium changes.</x:v>
+        <x:v>At 7.5x exit, about 16.23% premium ($58.21/share) reaches 20% IRR; exact threshold 16.234532%.</x:v>
       </x:c>
       <x:c r="B16" s="2"/>
       <x:c r="C16" s="2"/>
@@ -6341,7 +6341,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="str">
-        <x:v>Actual capital structure may flex with premium, ratings constraints, and credit-market pricing.</x:v>
+        <x:v>Debt terms may change with premium, ratings or market pricing. At 25% premium and 8.5x exit, IRR is 19.9942%, below 20%.</x:v>
       </x:c>
       <x:c r="B17" s="2"/>
       <x:c r="C17" s="2"/>
@@ -6389,7 +6389,7 @@
   <x:sheetData>
     <x:row r="1" ht="23" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>SOURCES, LIMITATIONS AND AUDIT TRAIL</x:v>
+        <x:v>SOURCES AND MODEL LIMITATIONS</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -6588,7 +6588,7 @@
         <x:v>Acquired cash</x:v>
       </x:c>
       <x:c r="B18" s="2" t="str">
-        <x:v>Cash $958.7m at Jun 30 2026 including $238.6m at foreign subsidiaries; not all deployability verified.</x:v>
+        <x:v>$958.7mm cash at June 30, 2026 includes $238.6mm held abroad. Full availability at closing is unverified.</x:v>
       </x:c>
       <x:c r="C18" s="2"/>
       <x:c r="D18" s="2"/>
@@ -6636,7 +6636,7 @@
         <x:v>IRR hurdle / loan rates / offer premium</x:v>
       </x:c>
       <x:c r="B22" s="2" t="str">
-        <x:v>Analyst assumptions; NOT facts about lender terms or board offer.</x:v>
+        <x:v>Analyst assumptions, not lender terms or a board offer.</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
       <x:c r="D22" s="2"/>
@@ -6660,7 +6660,7 @@
         <x:v>Forward model / cash flows</x:v>
       </x:c>
       <x:c r="B24" s="2" t="str">
-        <x:v>Annual simplification, ignores intrayear tax-season revolver, individual debt covenants, OID, and integration costs.</x:v>
+        <x:v>Annual model excludes the seasonal revolver, debt covenants, OID and integration costs.</x:v>
       </x:c>
       <x:c r="C24" s="2"/>
       <x:c r="D24" s="2"/>
@@ -6684,7 +6684,7 @@
         <x:v>Return type</x:v>
       </x:c>
       <x:c r="B26" s="2" t="str">
-        <x:v>Five-year annualized gross sponsor equity IRR before fund fees, carry, financing funding timing.</x:v>
+        <x:v>Gross sponsor equity IRR before fees and carry. Case schedules use five years. B21 changes sensitivity only. Funding timing is simplified.</x:v>
       </x:c>
       <x:c r="C26" s="2"/>
       <x:c r="D26" s="2"/>
